--- a/tasks/finalpool/pw-canvas-enrollment-analysis-gsheet-word/groundtruth_workspace/Enrollment_Analysis_Report.xlsx
+++ b/tasks/finalpool/pw-canvas-enrollment-analysis-gsheet-word/groundtruth_workspace/Enrollment_Analysis_Report.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,26 +27,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -61,9 +48,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,27 +419,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Course</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Enrollment</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Avg_Score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Pass_Rate</t>
         </is>
@@ -471,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1993</v>
+        <v>383</v>
       </c>
       <c r="D2" t="n">
-        <v>83</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>83</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -492,13 +478,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>542</v>
+        <v>365</v>
       </c>
       <c r="D3" t="n">
-        <v>72</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="4">
@@ -513,13 +499,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>725</v>
+        <v>2237</v>
       </c>
       <c r="D4" t="n">
-        <v>85</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -534,13 +520,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2024</v>
+        <v>2292</v>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>65.7</v>
       </c>
       <c r="E5" t="n">
-        <v>74</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="6">
@@ -555,13 +541,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1920</v>
+        <v>1767</v>
       </c>
       <c r="D6" t="n">
-        <v>70</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="7">
@@ -576,13 +562,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1447</v>
+        <v>1613</v>
       </c>
       <c r="D7" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>77</v>
+        <v>94.5</v>
       </c>
     </row>
   </sheetData>
@@ -600,12 +586,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -628,7 +614,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8651</v>
+        <v>8657</v>
       </c>
     </row>
     <row r="4">
@@ -638,7 +624,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76.8</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="5">
@@ -648,7 +634,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75.2</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -666,17 +652,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Course</t>
         </is>
@@ -693,7 +679,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Biochemistry &amp; Bioinformatics (Spring 2013)</t>
+          <t>Biochemistry &amp; Bioinformatics (Fall 2014)</t>
         </is>
       </c>
     </row>
@@ -708,7 +694,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Applied Analytics &amp; Algorithms (Fall 2013)</t>
+          <t>Biochemistry &amp; Bioinformatics (Fall 2013)</t>
         </is>
       </c>
     </row>
